--- a/French Ligue 1/Raw/25_26.xlsx
+++ b/French Ligue 1/Raw/25_26.xlsx
@@ -1464,132 +1464,132 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>43</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="T8" t="n">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="U8" t="n">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="V8" t="n">
-        <v>79</v>
+        <v>76.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
         <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AB8" t="n">
         <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>608</v>
+        <v>739</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
         <v>11</v>
       </c>
       <c r="AI8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>23</v>
       </c>
       <c r="AM8" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AN8" t="n">
-        <v>490</v>
+        <v>628</v>
       </c>
       <c r="AO8" t="n">
-        <v>406</v>
+        <v>542</v>
       </c>
       <c r="AP8" t="n">
-        <v>82.90000000000001</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="9">
@@ -1600,132 +1600,132 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>507</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>16</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14</v>
+      </c>
+      <c r="S9" t="n">
+        <v>56</v>
+      </c>
+      <c r="T9" t="n">
+        <v>386</v>
+      </c>
+      <c r="U9" t="n">
+        <v>305</v>
+      </c>
+      <c r="V9" t="n">
+        <v>79</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H9" t="n">
-        <v>16</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="Y9" t="n">
         <v>13</v>
-      </c>
-      <c r="K9" t="n">
-        <v>517</v>
-      </c>
-      <c r="L9" t="n">
-        <v>25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>35</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>52</v>
-      </c>
-      <c r="T9" t="n">
-        <v>379</v>
-      </c>
-      <c r="U9" t="n">
-        <v>289</v>
-      </c>
-      <c r="V9" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>9</v>
       </c>
       <c r="Z9" t="n">
         <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AB9" t="n">
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>739</v>
+        <v>608</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH9" t="n">
         <v>11</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
         <v>23</v>
       </c>
       <c r="AM9" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AN9" t="n">
-        <v>628</v>
+        <v>490</v>
       </c>
       <c r="AO9" t="n">
-        <v>542</v>
+        <v>406</v>
       </c>
       <c r="AP9" t="n">
-        <v>86.3</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2552,132 +2552,132 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
         <v>7</v>
       </c>
       <c r="J16" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>681</v>
+        <v>629</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
+        <v>21</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>19</v>
+      </c>
+      <c r="S16" t="n">
+        <v>47</v>
+      </c>
+      <c r="T16" t="n">
+        <v>496</v>
+      </c>
+      <c r="U16" t="n">
+        <v>418</v>
+      </c>
+      <c r="V16" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>9</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>28</v>
-      </c>
-      <c r="S16" t="n">
-        <v>61</v>
-      </c>
-      <c r="T16" t="n">
-        <v>591</v>
-      </c>
-      <c r="U16" t="n">
-        <v>476</v>
-      </c>
-      <c r="V16" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5</v>
       </c>
       <c r="Z16" t="n">
         <v>2</v>
       </c>
       <c r="AA16" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>624</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH16" t="n">
         <v>16</v>
       </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>576</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>14</v>
-      </c>
       <c r="AI16" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AM16" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AN16" t="n">
-        <v>430</v>
+        <v>519</v>
       </c>
       <c r="AO16" t="n">
-        <v>360</v>
+        <v>426</v>
       </c>
       <c r="AP16" t="n">
-        <v>83.7</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -2688,132 +2688,132 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
         <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>629</v>
+        <v>681</v>
       </c>
       <c r="L17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>7</v>
       </c>
-      <c r="N17" t="n">
-        <v>11</v>
-      </c>
-      <c r="O17" t="n">
-        <v>21</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
       <c r="R17" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="S17" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="T17" t="n">
-        <v>496</v>
+        <v>591</v>
       </c>
       <c r="U17" t="n">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="V17" t="n">
-        <v>84.3</v>
+        <v>80.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AB17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AC17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>576</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH17" t="n">
         <v>14</v>
       </c>
-      <c r="AE17" t="n">
-        <v>624</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16</v>
-      </c>
       <c r="AI17" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AN17" t="n">
-        <v>519</v>
+        <v>430</v>
       </c>
       <c r="AO17" t="n">
-        <v>426</v>
+        <v>360</v>
       </c>
       <c r="AP17" t="n">
-        <v>82.09999999999999</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="18">

--- a/French Ligue 1/Raw/25_26.xlsx
+++ b/French Ligue 1/Raw/25_26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP28"/>
+  <dimension ref="A1:AP37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,6 +4310,1230 @@
       </c>
       <c r="AP28" t="n">
         <v>76.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>18</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" t="n">
+        <v>895</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>22</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>12</v>
+      </c>
+      <c r="S29" t="n">
+        <v>26</v>
+      </c>
+      <c r="T29" t="n">
+        <v>834</v>
+      </c>
+      <c r="U29" t="n">
+        <v>766</v>
+      </c>
+      <c r="V29" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>414</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>323</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>272</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>59</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>27</v>
+      </c>
+      <c r="K30" t="n">
+        <v>650</v>
+      </c>
+      <c r="L30" t="n">
+        <v>16</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>25</v>
+      </c>
+      <c r="P30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>9</v>
+      </c>
+      <c r="R30" t="n">
+        <v>16</v>
+      </c>
+      <c r="S30" t="n">
+        <v>63</v>
+      </c>
+      <c r="T30" t="n">
+        <v>545</v>
+      </c>
+      <c r="U30" t="n">
+        <v>454</v>
+      </c>
+      <c r="V30" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>476</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>380</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>296</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>77.90000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" t="n">
+        <v>453</v>
+      </c>
+      <c r="L31" t="n">
+        <v>25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14</v>
+      </c>
+      <c r="O31" t="n">
+        <v>35</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>10</v>
+      </c>
+      <c r="S31" t="n">
+        <v>59</v>
+      </c>
+      <c r="T31" t="n">
+        <v>304</v>
+      </c>
+      <c r="U31" t="n">
+        <v>211</v>
+      </c>
+      <c r="V31" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>68</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>754</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>33</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>637</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>527</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>69</v>
+      </c>
+      <c r="H32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>27</v>
+      </c>
+      <c r="K32" t="n">
+        <v>715</v>
+      </c>
+      <c r="L32" t="n">
+        <v>18</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>14</v>
+      </c>
+      <c r="O32" t="n">
+        <v>20</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>17</v>
+      </c>
+      <c r="S32" t="n">
+        <v>48</v>
+      </c>
+      <c r="T32" t="n">
+        <v>600</v>
+      </c>
+      <c r="U32" t="n">
+        <v>506</v>
+      </c>
+      <c r="V32" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>388</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>59</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>264</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>184</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>69.7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>49</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K33" t="n">
+        <v>591</v>
+      </c>
+      <c r="L33" t="n">
+        <v>17</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14</v>
+      </c>
+      <c r="O33" t="n">
+        <v>26</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>11</v>
+      </c>
+      <c r="R33" t="n">
+        <v>16</v>
+      </c>
+      <c r="S33" t="n">
+        <v>49</v>
+      </c>
+      <c r="T33" t="n">
+        <v>490</v>
+      </c>
+      <c r="U33" t="n">
+        <v>419</v>
+      </c>
+      <c r="V33" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>51</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>623</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>518</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>435</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>55</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>16</v>
+      </c>
+      <c r="K34" t="n">
+        <v>686</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>14</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>19</v>
+      </c>
+      <c r="S34" t="n">
+        <v>58</v>
+      </c>
+      <c r="T34" t="n">
+        <v>581</v>
+      </c>
+      <c r="U34" t="n">
+        <v>499</v>
+      </c>
+      <c r="V34" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>608</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>476</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>409</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>85.90000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>68</v>
+      </c>
+      <c r="H35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>905</v>
+      </c>
+      <c r="L35" t="n">
+        <v>14</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>11</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>20</v>
+      </c>
+      <c r="S35" t="n">
+        <v>40</v>
+      </c>
+      <c r="T35" t="n">
+        <v>807</v>
+      </c>
+      <c r="U35" t="n">
+        <v>743</v>
+      </c>
+      <c r="V35" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>478</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>374</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>307</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>82.09999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>47</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>24</v>
+      </c>
+      <c r="K36" t="n">
+        <v>567</v>
+      </c>
+      <c r="L36" t="n">
+        <v>15</v>
+      </c>
+      <c r="M36" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>16</v>
+      </c>
+      <c r="O36" t="n">
+        <v>19</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>27</v>
+      </c>
+      <c r="S36" t="n">
+        <v>82</v>
+      </c>
+      <c r="T36" t="n">
+        <v>460</v>
+      </c>
+      <c r="U36" t="n">
+        <v>351</v>
+      </c>
+      <c r="V36" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>53</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>653</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>41</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>518</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>428</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>23</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>48</v>
+      </c>
+      <c r="H37" t="n">
+        <v>18</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>19</v>
+      </c>
+      <c r="K37" t="n">
+        <v>596</v>
+      </c>
+      <c r="L37" t="n">
+        <v>16</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>15</v>
+      </c>
+      <c r="S37" t="n">
+        <v>42</v>
+      </c>
+      <c r="T37" t="n">
+        <v>489</v>
+      </c>
+      <c r="U37" t="n">
+        <v>406</v>
+      </c>
+      <c r="V37" t="n">
+        <v>83</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>52</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>633</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>523</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>441</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>84.3</v>
       </c>
     </row>
   </sheetData>
